--- a/docentes/Silva Villegas Mario - Estadisticos 20232.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,69 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -591,16 +654,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.52</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +680,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -637,16 +706,19 @@
         <v>26</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>26</v>
       </c>
-      <c r="E4">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -702,16 +774,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>60.87</v>
+        <v>56.52</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -728,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -754,16 +826,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +875,190 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920177</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920188</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920359</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920007</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Silva Villegas Mario - Estadisticos 20232.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,25 +76,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>CABRERA</t>
@@ -103,16 +106,13 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -121,22 +121,10 @@
     <t>DAVID</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
     <t>ERIK OMAR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -774,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>56.52</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -800,16 +788,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -835,7 +823,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,16 +865,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920177</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,16 +888,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -923,16 +911,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920359</v>
+        <v>22330051920177</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -941,21 +929,21 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920192</v>
+        <v>22330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -964,21 +952,21 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920193</v>
+        <v>22330051920192</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -987,21 +975,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920007</v>
+        <v>22330051920193</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1010,52 +998,6 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920201</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920202</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>
